--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,6 +141,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>FASTQ</t>
+  </si>
+  <si>
+    <t>FASTQ File</t>
+  </si>
+  <si>
     <t>CRAM</t>
   </si>
   <si>
@@ -165,40 +171,34 @@
     <t>VCF</t>
   </si>
   <si>
+    <t>gVCF</t>
+  </si>
+  <si>
+    <t>gVCF File</t>
+  </si>
+  <si>
+    <t>TBI</t>
+  </si>
+  <si>
+    <t>TBI Index File</t>
+  </si>
+  <si>
     <t>TGZ</t>
   </si>
   <si>
     <t>TGZ Archive File</t>
   </si>
   <si>
-    <t>gVCF</t>
-  </si>
-  <si>
-    <t>gVCF File</t>
-  </si>
-  <si>
-    <t>TBI</t>
-  </si>
-  <si>
-    <t>TBI Index File</t>
-  </si>
-  <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>BW File</t>
+    <t>bigWig</t>
+  </si>
+  <si>
+    <t>bigWig File</t>
   </si>
   <si>
     <t>BED</t>
   </si>
   <si>
     <t>BED File</t>
-  </si>
-  <si>
-    <t>FASTQ</t>
-  </si>
-  <si>
-    <t>FASTQ File</t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -542,7 +542,7 @@
         <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>44</v>
@@ -581,7 +581,7 @@
         <v>49</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -590,7 +590,7 @@
         <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>51</v>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Level</t>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>BED File</t>
+  </si>
+  <si>
+    <t>CSV</t>
+  </si>
+  <si>
+    <t>CSV File</t>
   </si>
 </sst>
 </file>
@@ -508,7 +514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -657,6 +663,18 @@
       </c>
       <c r="D12" s="2"/>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-document-format.xlsx
+++ b/docs/CodeSystem-document-format.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>21</t>
   </si>
   <si>
     <t>Level</t>
@@ -205,6 +205,60 @@
   </si>
   <si>
     <t>CSV File</t>
+  </si>
+  <si>
+    <t>TSV</t>
+  </si>
+  <si>
+    <t>TSV File</t>
+  </si>
+  <si>
+    <t>POD5</t>
+  </si>
+  <si>
+    <t>POD5 File</t>
+  </si>
+  <si>
+    <t>HDF5</t>
+  </si>
+  <si>
+    <t>HDF5 File</t>
+  </si>
+  <si>
+    <t>cloupe</t>
+  </si>
+  <si>
+    <t>cloupe File</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>GFF File</t>
+  </si>
+  <si>
+    <t>GTF</t>
+  </si>
+  <si>
+    <t>GTF File</t>
+  </si>
+  <si>
+    <t>FAM</t>
+  </si>
+  <si>
+    <t>FAM Pedigree File</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>HTML File</t>
+  </si>
+  <si>
+    <t>JSON</t>
+  </si>
+  <si>
+    <t>JSON File</t>
   </si>
 </sst>
 </file>
@@ -514,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -675,6 +729,114 @@
       </c>
       <c r="D13" s="2"/>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
